--- a/TP2/tabla_descriptiva_TP2.xlsx
+++ b/TP2/tabla_descriptiva_TP2.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>Edad</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -492,29 +492,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ingreso_ppal</t>
+          <t>Ingreso ocupación principal</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>32641</v>
       </c>
       <c r="C3" t="n">
-        <v>768768.9</v>
+        <v>870894.25</v>
       </c>
       <c r="D3" t="n">
-        <v>784208.65</v>
+        <v>858952.21</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>300000</v>
+        <v>394200</v>
       </c>
       <c r="G3" t="n">
-        <v>600000</v>
+        <v>700000</v>
       </c>
       <c r="H3" t="n">
-        <v>1000000</v>
+        <v>1100000</v>
       </c>
       <c r="I3" t="n">
         <v>30000000</v>
@@ -523,29 +523,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ingreso_total</t>
+          <t>Ingreso total individual</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>31850</v>
       </c>
       <c r="C4" t="n">
-        <v>872329.63</v>
+        <v>988417.8199999999</v>
       </c>
       <c r="D4" t="n">
-        <v>866382.28</v>
+        <v>945692.6899999999</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>400000</v>
+        <v>459900</v>
       </c>
       <c r="G4" t="n">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="H4" t="n">
-        <v>1025000</v>
+        <v>1200000</v>
       </c>
       <c r="I4" t="n">
         <v>30000000</v>
@@ -554,17 +554,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cant_ocupaciones_ad</t>
+          <t>Cantidad de ocupaciones adicionales</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40830</v>
+        <v>40824</v>
       </c>
       <c r="C5" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="D5" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -579,13 +579,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tam_estab</t>
+          <t>Tamano del establecimiento (código)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -616,7 +616,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>edad2</t>
+          <t>Edad al cuadrado</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -647,7 +647,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>educ</t>
+          <t>Anos de educación</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -678,7 +678,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>horastrab</t>
+          <t>Horas trabajadas (jefe/a)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -709,7 +709,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>horastrabj</t>
+          <t>Horas trabajadas del jefe/a (hogar)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -740,7 +740,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nhogar</t>
+          <t>Miembros del hogar</t>
         </is>
       </c>
       <c r="B11" t="n">
